--- a/AAII_Financials/Quarterly/ISDAY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ISDAY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="92">
   <si>
     <t>ISDAY</t>
   </si>
@@ -305,7 +305,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="[$-409]d\-mmm\-yy;@"/>
+    <numFmt numFmtId="164" formatCode="[$-409]d\-mmm\-yy;@"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -347,7 +347,7 @@
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -656,56 +656,59 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:K102"/>
+  <dimension ref="A5:L102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="11" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="12" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -733,8 +736,11 @@
       <c r="K8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -762,8 +768,11 @@
       <c r="K9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -791,8 +800,11 @@
       <c r="K10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -804,8 +816,9 @@
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L11" s="3"/>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -833,8 +846,11 @@
       <c r="K12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -862,8 +878,11 @@
       <c r="K13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -891,8 +910,11 @@
       <c r="K14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -920,8 +942,11 @@
       <c r="K15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -930,8 +955,9 @@
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
-    </row>
-    <row r="17" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L16" s="3"/>
+    </row>
+    <row r="17" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -959,8 +985,11 @@
       <c r="K17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -988,8 +1017,11 @@
       <c r="K18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1001,8 +1033,9 @@
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
-    </row>
-    <row r="20" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L19" s="3"/>
+    </row>
+    <row r="20" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1030,8 +1063,11 @@
       <c r="K20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1059,8 +1095,11 @@
       <c r="K21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1088,8 +1127,11 @@
       <c r="K22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1117,8 +1159,11 @@
       <c r="K23" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1146,8 +1191,11 @@
       <c r="K24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1175,8 +1223,11 @@
       <c r="K25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1204,8 +1255,11 @@
       <c r="K26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1233,8 +1287,11 @@
       <c r="K27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1262,8 +1319,11 @@
       <c r="K28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1291,8 +1351,11 @@
       <c r="K29" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1320,8 +1383,11 @@
       <c r="K30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1349,8 +1415,11 @@
       <c r="K31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1378,8 +1447,11 @@
       <c r="K32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1407,8 +1479,11 @@
       <c r="K33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1436,8 +1511,11 @@
       <c r="K34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1465,42 +1543,48 @@
       <c r="K35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="39" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1512,8 +1596,9 @@
       <c r="I39" s="3"/>
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
-    </row>
-    <row r="40" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L39" s="3"/>
+    </row>
+    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1525,71 +1610,78 @@
       <c r="I40" s="3"/>
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
-    </row>
-    <row r="41" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L40" s="3"/>
+    </row>
+    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>15668700</v>
+      </c>
+      <c r="E41" s="3">
         <v>15398000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>12324800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>12474800</v>
       </c>
-      <c r="G41" s="3">
-        <v>13513200</v>
-      </c>
       <c r="H41" s="3">
+        <v>11167400</v>
+      </c>
+      <c r="I41" s="3">
         <v>14859700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>15038800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>16427000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>18305600</v>
       </c>
     </row>
-    <row r="42" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>7244300</v>
+      </c>
+      <c r="E42" s="3">
         <v>5884100</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>5049500</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>5081500</v>
       </c>
-      <c r="G42" s="3">
-        <v>5613500</v>
-      </c>
       <c r="H42" s="3">
+        <v>7473100</v>
+      </c>
+      <c r="I42" s="3">
         <v>6185800</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>6185000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>5742900</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>4282900</v>
       </c>
     </row>
-    <row r="43" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3" t="s">
-        <v>4</v>
+      <c r="D43" s="3">
+        <v>237800</v>
       </c>
       <c r="E43" s="3" t="s">
         <v>4</v>
@@ -1597,23 +1689,26 @@
       <c r="F43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G43" s="3">
+      <c r="G43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H43" s="3">
         <v>316300</v>
       </c>
-      <c r="H43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="I43" s="3" t="s">
         <v>4</v>
       </c>
       <c r="J43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K43" s="3">
+      <c r="K43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L43" s="3">
         <v>178300</v>
       </c>
     </row>
-    <row r="44" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -1641,13 +1736,16 @@
       <c r="K44" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="45" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L44" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>4</v>
+      <c r="D45" s="3">
+        <v>125200</v>
       </c>
       <c r="E45" s="3" t="s">
         <v>4</v>
@@ -1655,139 +1753,154 @@
       <c r="F45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G45" s="3">
+      <c r="G45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H45" s="3">
         <v>134400</v>
       </c>
-      <c r="H45" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="I45" s="3" t="s">
         <v>4</v>
       </c>
       <c r="J45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L45" s="3">
         <v>90200</v>
       </c>
     </row>
-    <row r="46" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>23680100</v>
+      </c>
+      <c r="E46" s="3">
         <v>21282100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>17374300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>17556300</v>
       </c>
-      <c r="G46" s="3">
-        <v>20250500</v>
-      </c>
       <c r="H46" s="3">
+        <v>19764300</v>
+      </c>
+      <c r="I46" s="3">
         <v>21045600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>21223800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>22169900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>23220700</v>
       </c>
     </row>
-    <row r="47" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>15629700</v>
+      </c>
+      <c r="E47" s="3">
         <v>15265100</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>14188200</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>13333700</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>14439000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>12095600</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>12472100</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>12636800</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>12216800</v>
       </c>
     </row>
-    <row r="48" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1226100</v>
+      </c>
+      <c r="E48" s="3">
         <v>1244200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1221000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1234600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1154600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1180300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1143000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1122800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1095800</v>
       </c>
     </row>
-    <row r="49" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>480200</v>
+      </c>
+      <c r="E49" s="3">
         <v>43300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>42800</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>43600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>463200</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>42500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>43600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>45100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>403300</v>
       </c>
     </row>
-    <row r="50" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1815,8 +1928,11 @@
       <c r="K50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -1844,37 +1960,43 @@
       <c r="K51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>252000</v>
+      </c>
+      <c r="E52" s="3">
         <v>1727100</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>1699600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1798500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>250700</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>1675100</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>1625000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1651300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>252000</v>
       </c>
     </row>
-    <row r="53" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -1902,37 +2024,43 @@
       <c r="K53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>119852800</v>
+      </c>
+      <c r="E54" s="3">
         <v>114847300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>106582000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>105660100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>109883700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>104662100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>105502500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>107930900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>107145000</v>
       </c>
     </row>
-    <row r="55" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -1944,8 +2072,9 @@
       <c r="I55" s="3"/>
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
-    </row>
-    <row r="56" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L55" s="3"/>
+    </row>
+    <row r="56" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -1957,71 +2086,78 @@
       <c r="I56" s="3"/>
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
-    </row>
-    <row r="57" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L56" s="3"/>
+    </row>
+    <row r="57" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>93190300</v>
+      </c>
+      <c r="E57" s="3">
         <v>89245200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>83526900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>83218000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>85769000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>82088800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>82664700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>85615600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>87493100</v>
       </c>
     </row>
-    <row r="58" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>6369100</v>
+      </c>
+      <c r="E58" s="3">
         <v>5798800</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>4747000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>3828500</v>
       </c>
-      <c r="G58" s="3">
-        <v>6457400</v>
-      </c>
       <c r="H58" s="3">
+        <v>6437400</v>
+      </c>
+      <c r="I58" s="3">
         <v>5886400</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>5614700</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>4956000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>3761900</v>
       </c>
     </row>
-    <row r="59" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3" t="s">
-        <v>4</v>
+      <c r="D59" s="3">
+        <v>3575200</v>
       </c>
       <c r="E59" s="3" t="s">
         <v>4</v>
@@ -2029,110 +2165,122 @@
       <c r="F59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G59" s="3">
+      <c r="G59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H59" s="3">
         <v>3008900</v>
       </c>
-      <c r="H59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="I59" s="3" t="s">
         <v>4</v>
       </c>
       <c r="J59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K59" s="3">
+      <c r="K59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L59" s="3">
         <v>3055500</v>
       </c>
     </row>
-    <row r="60" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>103551600</v>
+      </c>
+      <c r="E60" s="3">
         <v>95090500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>88321400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>87096200</v>
       </c>
-      <c r="G60" s="3">
-        <v>95653000</v>
-      </c>
       <c r="H60" s="3">
+        <v>95633000</v>
+      </c>
+      <c r="I60" s="3">
         <v>88016400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>88324400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>90618100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>94676800</v>
       </c>
     </row>
-    <row r="61" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>5860000</v>
+      </c>
+      <c r="E61" s="3">
         <v>5586900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>4827800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>4833200</v>
       </c>
-      <c r="G61" s="3">
-        <v>4597000</v>
-      </c>
       <c r="H61" s="3">
+        <v>4616900</v>
+      </c>
+      <c r="I61" s="3">
         <v>4253800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>4437200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>4205300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>3818800</v>
       </c>
     </row>
-    <row r="62" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>744900</v>
+      </c>
+      <c r="E62" s="3">
         <v>5114200</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>4748300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>5049800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>840000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>4451300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>4752500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>5109200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>711300</v>
       </c>
     </row>
-    <row r="63" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2160,8 +2308,11 @@
       <c r="K63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2189,8 +2340,11 @@
       <c r="K64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2218,37 +2372,43 @@
       <c r="K65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>110769300</v>
+      </c>
+      <c r="E66" s="3">
         <v>106228200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>98312900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>97472900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>101764900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>97218600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>98048600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>100479700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>99899300</v>
       </c>
     </row>
-    <row r="67" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2260,8 +2420,9 @@
       <c r="I67" s="3"/>
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
-    </row>
-    <row r="68" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L67" s="3"/>
+    </row>
+    <row r="68" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2289,8 +2450,11 @@
       <c r="K68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2318,8 +2482,11 @@
       <c r="K69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2347,8 +2514,11 @@
       <c r="K70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2376,37 +2546,43 @@
       <c r="K71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>7314100</v>
+      </c>
+      <c r="E72" s="3">
         <v>6976000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>6668600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>6602900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>6528800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>5955400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>5992200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>5974400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>5798100</v>
       </c>
     </row>
-    <row r="73" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2434,8 +2610,11 @@
       <c r="K73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2463,8 +2642,11 @@
       <c r="K74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2492,37 +2674,43 @@
       <c r="K75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>8667300</v>
+      </c>
+      <c r="E76" s="3">
         <v>8396100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>8054200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>7971600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>7906600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>7241600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>7274500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>7269100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>7075600</v>
       </c>
     </row>
-    <row r="77" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2550,42 +2738,48 @@
       <c r="K77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="81" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -2613,8 +2807,11 @@
       <c r="K81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2626,37 +2823,41 @@
       <c r="I82" s="3"/>
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
-    </row>
-    <row r="83" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L82" s="3"/>
+    </row>
+    <row r="83" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>-68600</v>
+      </c>
+      <c r="E83" s="3">
         <v>44300</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>39600</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>41800</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>-63100</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>40400</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>40300</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>43800</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>-67500</v>
       </c>
     </row>
-    <row r="84" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2684,8 +2885,11 @@
       <c r="K84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2713,8 +2917,11 @@
       <c r="K85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -2742,8 +2949,11 @@
       <c r="K86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -2771,8 +2981,11 @@
       <c r="K87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -2800,37 +3013,43 @@
       <c r="K88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>619400</v>
+      </c>
+      <c r="E89" s="3">
         <v>-166000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-51300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>754900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>951900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>263800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-530200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-126500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-189100</v>
       </c>
     </row>
-    <row r="90" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -2842,37 +3061,41 @@
       <c r="I90" s="3"/>
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
-    </row>
-    <row r="91" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L90" s="3"/>
+    </row>
+    <row r="91" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-78800</v>
+      </c>
+      <c r="E91" s="3">
         <v>-49500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-52100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-45800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-45500</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-89400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-102600</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-85800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-84200</v>
       </c>
     </row>
-    <row r="92" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -2900,8 +3123,11 @@
       <c r="K92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -2929,37 +3155,43 @@
       <c r="K93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-910700</v>
+      </c>
+      <c r="E94" s="3">
         <v>-3135100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-2772300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-352100</v>
       </c>
-      <c r="G94" s="3">
-        <v>-1733500</v>
-      </c>
       <c r="H94" s="3">
+        <v>-1944600</v>
+      </c>
+      <c r="I94" s="3">
         <v>-1624200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1128000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-3572400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1520100</v>
       </c>
     </row>
-    <row r="95" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -2971,37 +3203,41 @@
       <c r="I95" s="3"/>
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
-    </row>
-    <row r="96" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L95" s="3"/>
+    </row>
+    <row r="96" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>93600</v>
+      </c>
+      <c r="E96" s="3">
         <v>84200</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>83700</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>49800</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>33900</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>93300</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>102600</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>52400</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>50900</v>
       </c>
     </row>
-    <row r="97" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3029,8 +3265,11 @@
       <c r="K97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3058,8 +3297,11 @@
       <c r="K98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3087,91 +3329,103 @@
       <c r="K99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>2181900</v>
+      </c>
+      <c r="E100" s="3">
         <v>6163300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>2916500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-1634100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-814200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>1545800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>779500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>1940900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-108100</v>
       </c>
     </row>
-    <row r="101" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-93000</v>
+      </c>
+      <c r="E101" s="3">
         <v>31500</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>38000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>8900</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>223000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>7600</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-17200</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-24400</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-54300</v>
       </c>
     </row>
-    <row r="102" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>1810100</v>
+      </c>
+      <c r="E102" s="3">
         <v>2883000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>123500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-1229400</v>
       </c>
-      <c r="G102" s="3">
-        <v>-1688800</v>
-      </c>
       <c r="H102" s="3">
+        <v>-1899900</v>
+      </c>
+      <c r="I102" s="3">
         <v>216800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-840600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-1749000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-1594300</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ISDAY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ISDAY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="92">
   <si>
     <t>ISDAY</t>
   </si>
@@ -656,59 +656,62 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:L102"/>
+  <dimension ref="A5:M102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="12" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="13" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -739,8 +742,11 @@
       <c r="L8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -771,8 +777,11 @@
       <c r="L9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -803,8 +812,11 @@
       <c r="L10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -817,8 +829,9 @@
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M11" s="3"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -849,8 +862,11 @@
       <c r="L12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -881,8 +897,11 @@
       <c r="L13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -913,8 +932,11 @@
       <c r="L14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -945,8 +967,11 @@
       <c r="L15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -956,8 +981,9 @@
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
-    </row>
-    <row r="17" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M16" s="3"/>
+    </row>
+    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -988,8 +1014,11 @@
       <c r="L17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1020,8 +1049,11 @@
       <c r="L18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1034,8 +1066,9 @@
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
-    </row>
-    <row r="20" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M19" s="3"/>
+    </row>
+    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1066,8 +1099,11 @@
       <c r="L20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1098,8 +1134,11 @@
       <c r="L21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1130,8 +1169,11 @@
       <c r="L22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1162,8 +1204,11 @@
       <c r="L23" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1194,8 +1239,11 @@
       <c r="L24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1226,8 +1274,11 @@
       <c r="L25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1258,8 +1309,11 @@
       <c r="L26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1290,8 +1344,11 @@
       <c r="L27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1322,8 +1379,11 @@
       <c r="L28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1354,8 +1414,11 @@
       <c r="L29" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1386,8 +1449,11 @@
       <c r="L30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1418,8 +1484,11 @@
       <c r="L31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1450,8 +1519,11 @@
       <c r="L32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1482,8 +1554,11 @@
       <c r="L33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1514,8 +1589,11 @@
       <c r="L34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1546,45 +1624,51 @@
       <c r="L35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1597,8 +1681,9 @@
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
-    </row>
-    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M39" s="3"/>
+    </row>
+    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1611,104 +1696,114 @@
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
-    </row>
-    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M40" s="3"/>
+    </row>
+    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>13929600</v>
+      </c>
+      <c r="E41" s="3">
         <v>15668700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>15398000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>12324800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>12474800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>11167400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>14859700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>15038800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>16427000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>18305600</v>
       </c>
     </row>
-    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>6317700</v>
+      </c>
+      <c r="E42" s="3">
         <v>7244300</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>5884100</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>5049500</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>5081500</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>7473100</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>6185800</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>6185000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>5742900</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>4282900</v>
       </c>
     </row>
-    <row r="43" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3">
+      <c r="D43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E43" s="3">
         <v>237800</v>
       </c>
-      <c r="E43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="F43" s="3" t="s">
         <v>4</v>
       </c>
       <c r="G43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H43" s="3">
+      <c r="H43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I43" s="3">
         <v>316300</v>
       </c>
-      <c r="I43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="J43" s="3" t="s">
         <v>4</v>
       </c>
       <c r="K43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L43" s="3">
+      <c r="L43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M43" s="3">
         <v>178300</v>
       </c>
     </row>
-    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -1739,168 +1834,186 @@
       <c r="L44" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M44" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E45" s="3">
         <v>125200</v>
       </c>
-      <c r="E45" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="F45" s="3" t="s">
         <v>4</v>
       </c>
       <c r="G45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H45" s="3">
+      <c r="H45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I45" s="3">
         <v>134400</v>
       </c>
-      <c r="I45" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="J45" s="3" t="s">
         <v>4</v>
       </c>
       <c r="K45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L45" s="3">
+      <c r="L45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M45" s="3">
         <v>90200</v>
       </c>
     </row>
-    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>20896700</v>
+      </c>
+      <c r="E46" s="3">
         <v>23680100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>21282100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>17374300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>17556300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>19764300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>21045600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>21223800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>22169900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>23220700</v>
       </c>
     </row>
-    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>15758000</v>
+      </c>
+      <c r="E47" s="3">
         <v>15629700</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>15265100</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>14188200</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>13333700</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>14439000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>12095600</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>12472100</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>12636800</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>12216800</v>
       </c>
     </row>
-    <row r="48" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1266600</v>
+      </c>
+      <c r="E48" s="3">
         <v>1226100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1244200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1221000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1234600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1154600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1180300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1143000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1122800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1095800</v>
       </c>
     </row>
-    <row r="49" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>43000</v>
+      </c>
+      <c r="E49" s="3">
         <v>480200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>43300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>42800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>43600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>463200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>42500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>43600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>45100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>403300</v>
       </c>
     </row>
-    <row r="50" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1931,8 +2044,11 @@
       <c r="L50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -1963,40 +2079,46 @@
       <c r="L51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1728700</v>
+      </c>
+      <c r="E52" s="3">
         <v>252000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>1727100</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1699600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1798500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>250700</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>1675100</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1625000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1651300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>252000</v>
       </c>
     </row>
-    <row r="53" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2027,40 +2149,46 @@
       <c r="L53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>116980500</v>
+      </c>
+      <c r="E54" s="3">
         <v>119852800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>114847300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>106582000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>105660100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>109883700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>104662100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>105502500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>107930900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>107145000</v>
       </c>
     </row>
-    <row r="55" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2073,8 +2201,9 @@
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
-    </row>
-    <row r="56" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M55" s="3"/>
+    </row>
+    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2087,200 +2216,219 @@
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
-    </row>
-    <row r="57" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M56" s="3"/>
+    </row>
+    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>89496700</v>
+      </c>
+      <c r="E57" s="3">
         <v>93190300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>89245200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>83526900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>83218000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>85769000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>82088800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>82664700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>85615600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>87493100</v>
       </c>
     </row>
-    <row r="58" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>6649400</v>
+      </c>
+      <c r="E58" s="3">
         <v>6369100</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>5798800</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>4747000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>3828500</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>6437400</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>5886400</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>5614700</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>4956000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>3761900</v>
       </c>
     </row>
-    <row r="59" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
+      <c r="D59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E59" s="3">
         <v>3575200</v>
       </c>
-      <c r="E59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="F59" s="3" t="s">
         <v>4</v>
       </c>
       <c r="G59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H59" s="3">
+      <c r="H59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I59" s="3">
         <v>3008900</v>
       </c>
-      <c r="I59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="J59" s="3" t="s">
         <v>4</v>
       </c>
       <c r="K59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L59" s="3">
+      <c r="L59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M59" s="3">
         <v>3055500</v>
       </c>
     </row>
-    <row r="60" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>96146100</v>
+      </c>
+      <c r="E60" s="3">
         <v>103551600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>95090500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>88321400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>87096200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>95633000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>88016400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>88324400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>90618100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>94676800</v>
       </c>
     </row>
-    <row r="61" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>5682300</v>
+      </c>
+      <c r="E61" s="3">
         <v>5860000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>5586900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>4827800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>4833200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>4616900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>4253800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>4437200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>4205300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>3818800</v>
       </c>
     </row>
-    <row r="62" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>6011300</v>
+      </c>
+      <c r="E62" s="3">
         <v>744900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>5114200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>4748300</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>5049800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>840000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>4451300</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>4752500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>5109200</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>711300</v>
       </c>
     </row>
-    <row r="63" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2311,8 +2459,11 @@
       <c r="L63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2343,8 +2494,11 @@
       <c r="L64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2375,40 +2529,46 @@
       <c r="L65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>107839700</v>
+      </c>
+      <c r="E66" s="3">
         <v>110769300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>106228200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>98312900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>97472900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>101764900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>97218600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>98048600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>100479700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>99899300</v>
       </c>
     </row>
-    <row r="67" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2421,8 +2581,9 @@
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
-    </row>
-    <row r="68" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M67" s="3"/>
+    </row>
+    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2453,8 +2614,11 @@
       <c r="L68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2485,8 +2649,11 @@
       <c r="L69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2517,8 +2684,11 @@
       <c r="L70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2549,40 +2719,46 @@
       <c r="L71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3">
+      <c r="D72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E72" s="3">
         <v>7314100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>6976000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>6668600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>6602900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>6528800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>5955400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>5992200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>5974400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>5798100</v>
       </c>
     </row>
-    <row r="73" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2613,8 +2789,11 @@
       <c r="L73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2645,8 +2824,11 @@
       <c r="L74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2677,40 +2859,46 @@
       <c r="L75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>8717600</v>
+      </c>
+      <c r="E76" s="3">
         <v>8667300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>8396100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>8054200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>7971600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>7906600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>7241600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>7274500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>7269100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>7075600</v>
       </c>
     </row>
-    <row r="77" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2741,45 +2929,51 @@
       <c r="L77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="81" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -2810,8 +3004,11 @@
       <c r="L81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2824,40 +3021,44 @@
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
-    </row>
-    <row r="83" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M82" s="3"/>
+    </row>
+    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>46000</v>
+      </c>
+      <c r="E83" s="3">
         <v>-68600</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>44300</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>39600</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>41800</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>-63100</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>40400</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>40300</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>43800</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>-67500</v>
       </c>
     </row>
-    <row r="84" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2888,8 +3089,11 @@
       <c r="L84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2920,8 +3124,11 @@
       <c r="L85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -2952,8 +3159,11 @@
       <c r="L86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -2984,8 +3194,11 @@
       <c r="L87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3016,40 +3229,46 @@
       <c r="L88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>103400</v>
+      </c>
+      <c r="E89" s="3">
         <v>619400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-166000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-51300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>754900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>951900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>263800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-530200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-126500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-189100</v>
       </c>
     </row>
-    <row r="90" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3062,40 +3281,44 @@
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
-    </row>
-    <row r="91" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M90" s="3"/>
+    </row>
+    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-46700</v>
+      </c>
+      <c r="E91" s="3">
         <v>-78800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-49500</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-52100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-45800</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-45500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-89400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-102600</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-85800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-84200</v>
       </c>
     </row>
-    <row r="92" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3126,8 +3349,11 @@
       <c r="L92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3158,40 +3384,46 @@
       <c r="L93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-2200100</v>
+      </c>
+      <c r="E94" s="3">
         <v>-910700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-3135100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-2772300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-352100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1944600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1624200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1128000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-3572400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1520100</v>
       </c>
     </row>
-    <row r="95" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3204,40 +3436,44 @@
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
-    </row>
-    <row r="96" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M95" s="3"/>
+    </row>
+    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
+      <c r="D96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E96" s="3">
         <v>93600</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>84200</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>83700</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>49800</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>33900</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>93300</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>102600</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>52400</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>50900</v>
       </c>
     </row>
-    <row r="97" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3268,8 +3504,11 @@
       <c r="L97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3300,8 +3539,11 @@
       <c r="L98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3332,100 +3574,112 @@
       <c r="L99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-786400</v>
+      </c>
+      <c r="E100" s="3">
         <v>2181900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>6163300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>2916500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-1634100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-814200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>1545800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>779500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>1940900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-108100</v>
       </c>
     </row>
-    <row r="101" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E101" s="3">
         <v>-93000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>31500</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>38000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>8900</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>223000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>7600</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-17200</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-24400</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-54300</v>
       </c>
     </row>
-    <row r="102" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-2865900</v>
+      </c>
+      <c r="E102" s="3">
         <v>1810100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>2883000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>123500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-1229400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-1899900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>216800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-840600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-1749000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-1594300</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ISDAY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ISDAY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="391" uniqueCount="92">
   <si>
     <t>ISDAY</t>
   </si>
@@ -656,68 +656,71 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:O102"/>
+  <dimension ref="A5:P102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="15" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="16" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -757,8 +760,11 @@
       <c r="O8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -798,8 +804,11 @@
       <c r="O9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -839,8 +848,11 @@
       <c r="O10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -856,8 +868,9 @@
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P11" s="3"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -897,8 +910,11 @@
       <c r="O12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -938,8 +954,11 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -979,8 +998,11 @@
       <c r="O14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1020,8 +1042,11 @@
       <c r="O15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1034,8 +1059,9 @@
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
-    </row>
-    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P16" s="3"/>
+    </row>
+    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1075,8 +1101,11 @@
       <c r="O17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1116,8 +1145,11 @@
       <c r="O18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1133,8 +1165,9 @@
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
-    </row>
-    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P19" s="3"/>
+    </row>
+    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1174,8 +1207,11 @@
       <c r="O20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1215,8 +1251,11 @@
       <c r="O21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1256,8 +1295,11 @@
       <c r="O22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1297,8 +1339,11 @@
       <c r="O23" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1338,8 +1383,11 @@
       <c r="O24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1379,8 +1427,11 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1420,8 +1471,11 @@
       <c r="O26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1461,8 +1515,11 @@
       <c r="O27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1502,8 +1559,11 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1543,8 +1603,11 @@
       <c r="O29" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1584,8 +1647,11 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1625,8 +1691,11 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1666,8 +1735,11 @@
       <c r="O32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1707,8 +1779,11 @@
       <c r="O33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1748,8 +1823,11 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1789,54 +1867,60 @@
       <c r="O35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1852,8 +1936,9 @@
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
-    </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P39" s="3"/>
+    </row>
+    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1869,95 +1954,102 @@
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
-    </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P40" s="3"/>
+    </row>
+    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>18226500</v>
+      </c>
+      <c r="E41" s="3">
         <v>19792800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>17583800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>13806900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>15668700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>15398000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>12324800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>12474800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>11167400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>14859700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>15038800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>16427000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>18305600</v>
       </c>
     </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>10323100</v>
+      </c>
+      <c r="E42" s="3">
         <v>7197300</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>8324300</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>6440400</v>
       </c>
-      <c r="G42" s="3">
-        <v>7244300</v>
-      </c>
       <c r="H42" s="3">
+        <v>7241000</v>
+      </c>
+      <c r="I42" s="3">
         <v>5884100</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>5049500</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>5081500</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>7473100</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>6185800</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>6185000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>5742900</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>4282900</v>
       </c>
     </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3" t="s">
-        <v>4</v>
+      <c r="D43" s="3">
+        <v>206100</v>
       </c>
       <c r="E43" s="3" t="s">
         <v>4</v>
@@ -1965,11 +2057,11 @@
       <c r="F43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G43" s="3">
-        <v>237800</v>
-      </c>
-      <c r="H43" s="3" t="s">
-        <v>4</v>
+      <c r="G43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H43" s="3">
+        <v>221000</v>
       </c>
       <c r="I43" s="3" t="s">
         <v>4</v>
@@ -1977,23 +2069,26 @@
       <c r="J43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K43" s="3">
+      <c r="K43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L43" s="3">
         <v>316300</v>
       </c>
-      <c r="L43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M43" s="3" t="s">
         <v>4</v>
       </c>
       <c r="N43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O43" s="3">
+      <c r="O43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P43" s="3">
         <v>178300</v>
       </c>
     </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2033,25 +2128,28 @@
       <c r="O44" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P44" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>7360700</v>
+      </c>
+      <c r="E45" s="3">
         <v>6855100</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>6440800</v>
       </c>
-      <c r="F45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G45" s="3">
-        <v>125200</v>
-      </c>
-      <c r="H45" s="3" t="s">
-        <v>4</v>
+      <c r="G45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H45" s="3">
+        <v>6183200</v>
       </c>
       <c r="I45" s="3" t="s">
         <v>4</v>
@@ -2059,187 +2157,202 @@
       <c r="J45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L45" s="3">
         <v>134400</v>
       </c>
-      <c r="L45" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M45" s="3" t="s">
         <v>4</v>
       </c>
       <c r="N45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O45" s="3">
+      <c r="O45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P45" s="3">
         <v>90200</v>
       </c>
     </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>36463900</v>
+      </c>
+      <c r="E46" s="3">
         <v>33845200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>32348900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>20247300</v>
       </c>
-      <c r="G46" s="3">
-        <v>23680100</v>
-      </c>
       <c r="H46" s="3">
+        <v>29672200</v>
+      </c>
+      <c r="I46" s="3">
         <v>21282100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>17374300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>17556300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>19764300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>21045600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>21223800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>22169900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>23220700</v>
       </c>
     </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>19989600</v>
+      </c>
+      <c r="E47" s="3">
         <v>18844800</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>18864200</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>15758000</v>
       </c>
-      <c r="G47" s="3">
-        <v>15629700</v>
-      </c>
       <c r="H47" s="3">
+        <v>15626700</v>
+      </c>
+      <c r="I47" s="3">
         <v>15265100</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>14188200</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>13333700</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>14439000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>12095600</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>12472100</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>12636800</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>12216800</v>
       </c>
     </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1192600</v>
+      </c>
+      <c r="E48" s="3">
         <v>1230700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1209700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1266600</v>
       </c>
-      <c r="G48" s="3">
-        <v>1226100</v>
-      </c>
       <c r="H48" s="3">
+        <v>1092400</v>
+      </c>
+      <c r="I48" s="3">
         <v>1244200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1221000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1234600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1154600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1180300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1143000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1122800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1095800</v>
       </c>
     </row>
-    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>379900</v>
+      </c>
+      <c r="E49" s="3">
         <v>5400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>5300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>43000</v>
       </c>
-      <c r="G49" s="3">
-        <v>480200</v>
-      </c>
       <c r="H49" s="3">
+        <v>326400</v>
+      </c>
+      <c r="I49" s="3">
         <v>43300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>42800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>43600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>463200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>42500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>43600</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>45100</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>403300</v>
       </c>
     </row>
-    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2279,8 +2392,11 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2320,49 +2436,55 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>263200</v>
+      </c>
+      <c r="E52" s="3">
         <v>1601000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>1556100</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1728700</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>252000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>1727100</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>1699600</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1798500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>250700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1675100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1625000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1651300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>252000</v>
       </c>
     </row>
-    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2402,49 +2524,55 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>149983100</v>
+      </c>
+      <c r="E54" s="3">
         <v>142679500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>136825200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>116980500</v>
       </c>
-      <c r="G54" s="3">
-        <v>119852800</v>
-      </c>
       <c r="H54" s="3">
+        <v>121532800</v>
+      </c>
+      <c r="I54" s="3">
         <v>114847300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>106582000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>105660100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>109883700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>104662100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>105502500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>107930900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>107145000</v>
       </c>
     </row>
-    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2460,8 +2588,9 @@
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
-    </row>
-    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P55" s="3"/>
+    </row>
+    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2477,107 +2606,114 @@
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
-    </row>
-    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P56" s="3"/>
+    </row>
+    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>114224000</v>
+      </c>
+      <c r="E57" s="3">
         <v>108782900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>102111400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>89496700</v>
       </c>
-      <c r="G57" s="3">
-        <v>93190300</v>
-      </c>
       <c r="H57" s="3">
+        <v>92592600</v>
+      </c>
+      <c r="I57" s="3">
         <v>89245200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>83526900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>83218000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>85769000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>82088800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>82664700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>85615600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>87493100</v>
       </c>
     </row>
-    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>7802400</v>
+      </c>
+      <c r="E58" s="3">
         <v>8305400</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>9306700</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>6649400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>6369100</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>5798800</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>4747000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>3828500</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>6437400</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>5886400</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>5614700</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>4956000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>3761900</v>
       </c>
     </row>
-    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>6995000</v>
+      </c>
+      <c r="E59" s="3">
         <v>5976300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>5596700</v>
       </c>
-      <c r="F59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G59" s="3">
-        <v>3575200</v>
-      </c>
-      <c r="H59" s="3" t="s">
-        <v>4</v>
+      <c r="G59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H59" s="3">
+        <v>6221100</v>
       </c>
       <c r="I59" s="3" t="s">
         <v>4</v>
@@ -2585,146 +2721,158 @@
       <c r="J59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K59" s="3">
+      <c r="K59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L59" s="3">
         <v>3008900</v>
       </c>
-      <c r="L59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M59" s="3" t="s">
         <v>4</v>
       </c>
       <c r="N59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O59" s="3">
+      <c r="O59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P59" s="3">
         <v>3055500</v>
       </c>
     </row>
-    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>129332500</v>
+      </c>
+      <c r="E60" s="3">
         <v>123111700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>117066700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>96192600</v>
       </c>
-      <c r="G60" s="3">
-        <v>103551600</v>
-      </c>
       <c r="H60" s="3">
+        <v>105465000</v>
+      </c>
+      <c r="I60" s="3">
         <v>95090500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>88321400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>87096200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>95633000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>88016400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>88324400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>90618100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>94676800</v>
       </c>
     </row>
-    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>8390200</v>
+      </c>
+      <c r="E61" s="3">
         <v>6766600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>7029400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>5682300</v>
       </c>
-      <c r="G61" s="3">
-        <v>5860000</v>
-      </c>
       <c r="H61" s="3">
+        <v>5767500</v>
+      </c>
+      <c r="I61" s="3">
         <v>5586900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>4827800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>4833200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>4616900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>4253800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>4437200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>4205300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>3818800</v>
       </c>
     </row>
-    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>504400</v>
+      </c>
+      <c r="E62" s="3">
         <v>1733900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>2031900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>5523000</v>
       </c>
-      <c r="G62" s="3">
-        <v>744900</v>
-      </c>
       <c r="H62" s="3">
+        <v>644900</v>
+      </c>
+      <c r="I62" s="3">
         <v>5114200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>4748300</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>5049800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>840000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>4451300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>4752500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>5109200</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>711300</v>
       </c>
     </row>
-    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2764,8 +2912,11 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2805,8 +2956,11 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2846,49 +3000,55 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>138897400</v>
+      </c>
+      <c r="E66" s="3">
         <v>132089000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>126621900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>107839700</v>
       </c>
-      <c r="G66" s="3">
-        <v>110769300</v>
-      </c>
       <c r="H66" s="3">
+        <v>112449300</v>
+      </c>
+      <c r="I66" s="3">
         <v>106228200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>98312900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>97472900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>101764900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>97218600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>98048600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>100479700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>99899300</v>
       </c>
     </row>
-    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2904,8 +3064,9 @@
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
-    </row>
-    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P67" s="3"/>
+    </row>
+    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2945,8 +3106,11 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2986,8 +3150,11 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3027,8 +3194,11 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3068,49 +3238,55 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>9141200</v>
+      </c>
+      <c r="E72" s="3">
         <v>8713700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>8359300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>7348200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>7314100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>6976000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>6668600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>6602900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>6528800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>5955400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>5992200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>5974400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>5798100</v>
       </c>
     </row>
-    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3150,8 +3326,11 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3191,8 +3370,11 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3232,49 +3414,55 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>10605100</v>
+      </c>
+      <c r="E76" s="3">
         <v>10130800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>9757200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>8717600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>8667300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>8396100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>8054200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>7971600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>7906600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>7241600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>7274500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>7269100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>7075600</v>
       </c>
     </row>
-    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3314,54 +3502,60 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -3401,8 +3595,11 @@
       <c r="O81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3418,49 +3615,53 @@
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
-    </row>
-    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P82" s="3"/>
+    </row>
+    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>-40400</v>
+      </c>
+      <c r="E83" s="3">
         <v>47900</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>44900</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>46000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>-68600</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>44300</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>39600</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>41800</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>-63100</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>40400</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>40300</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>43800</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>-67500</v>
       </c>
     </row>
-    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3500,8 +3701,11 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3541,8 +3745,11 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3582,8 +3789,11 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3623,8 +3833,11 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3664,49 +3877,55 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-133600</v>
+      </c>
+      <c r="E89" s="3">
         <v>1266600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>801900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>54500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>619400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-166000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-51300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>754900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>951900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>263800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-530200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-126500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-189100</v>
       </c>
     </row>
-    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3722,49 +3941,53 @@
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
-    </row>
-    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P90" s="3"/>
+    </row>
+    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-58700</v>
+      </c>
+      <c r="E91" s="3">
         <v>-53800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-48100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-46700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-78800</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-49500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-52100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-45800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-45500</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-89400</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-102600</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-85800</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-84200</v>
       </c>
     </row>
-    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3804,8 +4027,11 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3845,49 +4071,55 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1803600</v>
+      </c>
+      <c r="E94" s="3">
         <v>-2750100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-2768800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-2200100</v>
       </c>
-      <c r="G94" s="3">
-        <v>-910700</v>
-      </c>
       <c r="H94" s="3">
+        <v>-1193500</v>
+      </c>
+      <c r="I94" s="3">
         <v>-3075900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-2733000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-172800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1944600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1624200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1128000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-3572400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-1520100</v>
       </c>
     </row>
-    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3903,49 +4135,53 @@
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
-    </row>
-    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P95" s="3"/>
+    </row>
+    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>177500</v>
+      </c>
+      <c r="E96" s="3">
         <v>134700</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>185800</v>
       </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
       <c r="G96" s="3">
+        <v>0</v>
+      </c>
+      <c r="H96" s="3">
         <v>93600</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>84200</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>83700</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>49800</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>33900</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>93300</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>102600</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>52400</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>50900</v>
       </c>
     </row>
-    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3985,8 +4221,11 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4026,8 +4265,11 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4067,127 +4309,139 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>1786400</v>
+      </c>
+      <c r="E100" s="3">
         <v>3562000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>4214200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-737700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>2181900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>6163300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>2916500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-1634100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-814200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>1545800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>779500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>1940900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-108100</v>
       </c>
     </row>
-    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-80400</v>
+      </c>
+      <c r="E101" s="3">
         <v>20700</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>30500</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>1900</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-93000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>31500</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>38000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>8900</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>223000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>7600</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-17200</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-24400</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-54300</v>
       </c>
     </row>
-    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-154300</v>
+      </c>
+      <c r="E102" s="3">
         <v>2054600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>2173400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-2865900</v>
       </c>
-      <c r="G102" s="3">
-        <v>1810100</v>
-      </c>
       <c r="H102" s="3">
+        <v>1527300</v>
+      </c>
+      <c r="I102" s="3">
         <v>2942200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>162800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-1050100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-1899900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>216800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-840600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-1749000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-1594300</v>
       </c>
     </row>
